--- a/artfynd/A 50011-2023 artfynd.xlsx
+++ b/artfynd/A 50011-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1154,6 +1154,117 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135482953</v>
+      </c>
+      <c r="B6" t="n">
+        <v>45048</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Horsvadbron, Olsfors, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>360762</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6396244</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ann-Christin Edhav</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ann-Christin Edhav</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50011-2023 artfynd.xlsx
+++ b/artfynd/A 50011-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132536477</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124750730</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1034,6 +1049,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93105144</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,6 +1173,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93133558</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1264,8 +1289,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135482953</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 50011-2023 artfynd.xlsx
+++ b/artfynd/A 50011-2023 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>135482953</v>
       </c>
       <c r="B6" t="n">
-        <v>45048</v>
+        <v>45053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50011-2023 artfynd.xlsx
+++ b/artfynd/A 50011-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,6 +1176,122 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/93133558</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135482953</v>
+      </c>
+      <c r="B6" t="n">
+        <v>45053</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>201164</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sexfläckig bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Zygaena filipendulae</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Horsvadbron, Olsfors, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>360762</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6396244</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bollebygd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ann-Christin Edhav</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ann-Christin Edhav</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135482953</t>
         </is>
       </c>
     </row>
@@ -1185,6 +1301,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50011-2023 artfynd.xlsx
+++ b/artfynd/A 50011-2023 artfynd.xlsx
@@ -1184,7 +1184,7 @@
         <v>135482953</v>
       </c>
       <c r="B6" t="n">
-        <v>45053</v>
+        <v>45055</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
